--- a/jira_export_TEST.xlsx
+++ b/jira_export_TEST.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>534 h</t>
+          <t>559 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="L16" s="15" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>3</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>910</v>
       </c>
       <c r="P61" s="13" t="n">
-        <v>330.91</v>
+        <v>191.58</v>
       </c>
     </row>
     <row r="62">
@@ -8081,7 +8081,7 @@
         <v>7</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>7</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>29.5</v>
+        <v>32</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>8</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>14</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>15</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>33</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>41374.78</v>
       </c>
       <c r="P172" s="19" t="n">
-        <v>118.47</v>
+        <v>114.69</v>
       </c>
     </row>
   </sheetData>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>196.5</v>
+        <v>206.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>41</v>
@@ -14140,17 +14140,17 @@
         <v>8</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>245.5</v>
+        <v>255.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>64.5</v>
+        <v>74.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>592.2</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>88.5</v>
+        <v>90</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>11.5</v>
@@ -14170,7 +14170,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>101</v>
+        <v>102.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>12</v>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.7%</t>
         </is>
       </c>
     </row>
@@ -14192,7 +14192,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>105.75</v>
+        <v>109.75</v>
       </c>
     </row>
   </sheetData>
@@ -14280,13 +14280,13 @@
         <v>373338</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>169146</v>
+        <v>167796</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>204192</v>
+        <v>205542</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>158201</v>
+        <v>159551</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>25780</v>
@@ -14305,13 +14305,13 @@
         <v>198097</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>96192</v>
+        <v>94842</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>101905</v>
+        <v>103255</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>92986</v>
+        <v>94336</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>4070</v>

--- a/jira_export_TEST.xlsx
+++ b/jira_export_TEST.xlsx
@@ -693,7 +693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Synthèse au 19/06/2026 (15/23 jours ouvrés écoulés)</t>
+          <t>Synthèse au 20/06/2026 (15/23 jours ouvrés écoulés)</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Backlog à date — 19/06/2026</t>
+          <t>Backlog à date — 20/06/2026</t>
         </is>
       </c>
     </row>

--- a/jira_export_TEST.xlsx
+++ b/jira_export_TEST.xlsx
@@ -693,7 +693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Synthèse au 20/06/2026 (15/23 jours ouvrés écoulés)</t>
+          <t>Synthèse au 21/06/2026 (15/23 jours ouvrés écoulés)</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Backlog à date — 20/06/2026</t>
+          <t>Backlog à date — 21/06/2026</t>
         </is>
       </c>
     </row>
